--- a/dc6_milk_run_routes.xlsx
+++ b/dc6_milk_run_routes.xlsx
@@ -515,7 +515,7 @@
         <v>16.26</v>
       </c>
       <c r="J2" t="n">
-        <v>865631.98</v>
+        <v>90731.98</v>
       </c>
     </row>
     <row r="3">
@@ -553,7 +553,7 @@
         <v>1091.43</v>
       </c>
       <c r="J3" t="n">
-        <v>1347019.53</v>
+        <v>456991.53</v>
       </c>
     </row>
     <row r="4">
@@ -591,7 +591,7 @@
         <v>83.19</v>
       </c>
       <c r="J4" t="n">
-        <v>1016214.99</v>
+        <v>126186.99</v>
       </c>
     </row>
     <row r="5">
@@ -629,7 +629,7 @@
         <v>410.75</v>
       </c>
       <c r="J5" t="n">
-        <v>1123686.87</v>
+        <v>233658.87</v>
       </c>
     </row>
   </sheetData>
